--- a/data/trans_dic/KIDM_C_3_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/KIDM_C_3_R-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores de los que se han reido mucho o muchísimo otros menores (autopercepción menor)</t>
+          <t>Menores de los que se han reido mucho o muchísimo otros menores (autopercepción menor) (tasa de respuesta: 94,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,07; 12,96</t>
+          <t>3,09; 13,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,1; 22,54</t>
+          <t>7,59; 22,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,94; 13,9</t>
+          <t>2,78; 13,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,93</t>
+          <t>0,0; 10,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,82; 11,93</t>
+          <t>2,61; 12,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,52; 13,18</t>
+          <t>3,49; 13,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,63; 19,07</t>
+          <t>5,54; 18,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 14,16</t>
+          <t>1,13; 13,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,29; 10,21</t>
+          <t>3,62; 10,31</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,4; 15,2</t>
+          <t>6,46; 15,03</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,61; 14,24</t>
+          <t>4,92; 13,66</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 8,79</t>
+          <t>1,0; 9,21</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,31; 11,19</t>
+          <t>3,18; 11,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,85; 19,11</t>
+          <t>7,78; 18,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,16; 12,51</t>
+          <t>4,64; 12,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,54; 15,14</t>
+          <t>2,37; 13,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 8,1</t>
+          <t>1,47; 8,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,98; 25,78</t>
+          <t>12,96; 26,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,59; 17,56</t>
+          <t>7,47; 17,63</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,0</t>
+          <t>0,0; 3,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,82; 8,01</t>
+          <t>3,09; 8,26</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,76; 20,35</t>
+          <t>11,74; 19,92</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,74; 13,63</t>
+          <t>6,47; 13,32</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,42</t>
+          <t>0,95; 5,56</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 10,41</t>
+          <t>1,15; 11,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,86; 28,74</t>
+          <t>12,76; 29,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,19; 17,79</t>
+          <t>4,75; 16,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,2</t>
+          <t>0,0; 6,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 8,21</t>
+          <t>0,78; 7,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,75; 17,22</t>
+          <t>5,56; 17,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,2; 17,22</t>
+          <t>4,81; 17,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,86</t>
+          <t>0,0; 3,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 7,62</t>
+          <t>1,54; 7,21</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,91; 21,01</t>
+          <t>10,09; 20,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,23; 14,98</t>
+          <t>5,88; 14,44</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 4,57</t>
+          <t>0,27; 4,38</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 9,45</t>
+          <t>1,01; 9,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,59; 24,26</t>
+          <t>9,83; 23,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,05; 17,93</t>
+          <t>7,04; 18,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 11,03</t>
+          <t>1,25; 11,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 8,39</t>
+          <t>1,46; 8,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,46; 14,99</t>
+          <t>4,76; 15,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,95; 13,16</t>
+          <t>3,48; 12,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,05</t>
+          <t>0,0; 11,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 6,74</t>
+          <t>2,02; 6,88</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,19; 17,08</t>
+          <t>8,65; 17,99</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,15; 13,46</t>
+          <t>6,37; 13,82</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,39; 7,9</t>
+          <t>1,34; 8,58</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,58; 7,76</t>
+          <t>3,53; 7,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,01; 18,83</t>
+          <t>11,93; 18,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,9; 12,01</t>
+          <t>6,5; 11,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,7; 6,96</t>
+          <t>1,71; 6,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,46; 6,11</t>
+          <t>2,6; 6,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,02; 14,99</t>
+          <t>8,87; 14,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,55; 13,27</t>
+          <t>7,49; 12,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,15</t>
+          <t>0,79; 3,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,57; 6,3</t>
+          <t>3,41; 6,25</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,31; 15,76</t>
+          <t>11,33; 15,8</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,83; 11,52</t>
+          <t>7,86; 11,51</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,17</t>
+          <t>1,76; 4,46</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores de los que se han reido mucho o muchísimo otros menores (autopercepción menor) (tasa de respuesta: 94,62%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3658</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8684</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4696</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>4265</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>5116</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>7879</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2293</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>7923</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>13800</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>12574</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2910</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1779; 7524</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4815; 14414</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1920; 9380</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3230</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1775; 8277</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2487; 9635</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>3933; 13202</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>542; 6577</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>4544; 12942</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>8700; 20252</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>6896; 19124</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>791; 7293</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>6311</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12178</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7985</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3555</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3397</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>17843</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>12380</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>9708</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>30021</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>20365</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>4195</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>3132; 10977</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>7608; 17821</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>4770; 13225</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1273; 7309</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1356; 7451</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>12251; 24595</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>7772; 18335</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3226</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>5891; 15739</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>22588; 38325</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>13383; 27561</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>1486; 8681</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2570</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>12786</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6797</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1523</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1773</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>7182</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>7504</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>427</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>4343</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>19968</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>14301</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>1949</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>637; 6330</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>8313; 19029</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3322; 11801</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4971</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>480; 4873</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3843; 12085</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>3588; 13111</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2036</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1806; 8437</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>13552; 27099</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>8492; 20872</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>362; 5973</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>3015</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>13840</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>12050</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2235</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3281</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>7726</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>7330</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1853</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>6296</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>21566</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>19380</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>4088</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>793; 7444</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>8425; 20003</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>7308; 18944</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>669; 6259</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1284; 7176</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>4235; 13783</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>3464; 12577</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 6400</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>3355; 11456</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>15102; 31408</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>12964; 28106</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>1475; 9422</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>15555</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>47488</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>31528</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>7930</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>12716</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>37868</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>35092</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>5213</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>28271</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>85356</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>66621</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>13143</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>10234; 22365</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>37239; 58394</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>22477; 40964</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>3597; 13483</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>8051; 19316</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>28717; 48243</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>26171; 44589</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2144; 10486</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>20429; 37446</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>72079; 100496</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>54592; 79978</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>8490; 21475</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/KIDM_C_3_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/KIDM_C_3_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores de los que se han reido mucho o muchísimo otros menores (autopercepción menor) (tasa de respuesta: 94,62%)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor) (tasa de respuesta: 94,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,09; 13,08</t>
+          <t>2,15; 12,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,59; 22,72</t>
+          <t>7,79; 22,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,78; 13,59</t>
+          <t>2,24; 13,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,36</t>
+          <t>0,0; 9,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,61; 12,18</t>
+          <t>2,85; 12,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,49; 13,51</t>
+          <t>3,47; 13,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,54; 18,58</t>
+          <t>5,72; 18,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,13; 13,7</t>
+          <t>0,0; 12,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,62; 10,31</t>
+          <t>3,69; 10,34</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,46; 15,03</t>
+          <t>6,54; 15,14</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,92; 13,66</t>
+          <t>5,13; 14,38</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 9,21</t>
+          <t>0,92; 9,44</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,18; 11,14</t>
+          <t>3,2; 11,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,78; 18,22</t>
+          <t>7,66; 18,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,64; 12,85</t>
+          <t>4,19; 12,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 13,63</t>
+          <t>2,5; 14,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 8,09</t>
+          <t>1,47; 8,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,96; 26,01</t>
+          <t>13,47; 25,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,47; 17,63</t>
+          <t>7,42; 17,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,15</t>
+          <t>0,0; 3,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,09; 8,26</t>
+          <t>2,93; 8,02</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,74; 19,92</t>
+          <t>12,09; 20,26</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,47; 13,32</t>
+          <t>7,09; 13,63</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,56</t>
+          <t>0,95; 6,06</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 11,37</t>
+          <t>1,15; 10,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,76; 29,2</t>
+          <t>12,89; 28,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,75; 16,88</t>
+          <t>5,24; 17,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,89</t>
+          <t>0,0; 8,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 7,94</t>
+          <t>0,78; 7,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,56; 17,49</t>
+          <t>5,45; 17,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,81; 17,57</t>
+          <t>5,16; 17,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,17</t>
+          <t>0,0; 3,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 7,21</t>
+          <t>1,62; 7,35</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,09; 20,19</t>
+          <t>10,2; 20,21</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,88; 14,44</t>
+          <t>5,96; 14,33</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 4,38</t>
+          <t>0,27; 4,26</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 9,51</t>
+          <t>0,93; 8,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,83; 23,33</t>
+          <t>9,91; 23,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,04; 18,24</t>
+          <t>6,43; 17,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 11,7</t>
+          <t>1,24; 11,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 8,14</t>
+          <t>1,46; 8,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,76; 15,5</t>
+          <t>4,17; 14,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,48; 12,64</t>
+          <t>3,66; 12,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,35</t>
+          <t>0,0; 11,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,02; 6,88</t>
+          <t>1,71; 7,1</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,65; 17,99</t>
+          <t>8,56; 17,35</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,37; 13,82</t>
+          <t>6,31; 13,8</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 8,58</t>
+          <t>1,39; 8,27</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,53; 7,71</t>
+          <t>3,44; 7,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,93; 18,71</t>
+          <t>12,33; 18,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,5; 11,85</t>
+          <t>6,74; 11,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,71; 6,41</t>
+          <t>1,84; 6,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,6; 6,24</t>
+          <t>2,46; 6,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,87; 14,9</t>
+          <t>8,91; 15,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,49; 12,77</t>
+          <t>7,6; 12,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,87</t>
+          <t>0,79; 3,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,41; 6,25</t>
+          <t>3,49; 6,2</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,33; 15,8</t>
+          <t>11,43; 15,74</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,86; 11,51</t>
+          <t>7,85; 11,46</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,46</t>
+          <t>1,53; 4,32</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores de los que se han reido mucho o muchísimo otros menores (autopercepción menor) (tasa de respuesta: 94,62%)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor) (tasa de respuesta: 94,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1779; 7524</t>
+          <t>1235; 7378</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4815; 14414</t>
+          <t>4944; 14254</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1920; 9380</t>
+          <t>1545; 9440</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3230</t>
+          <t>0; 3054</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1775; 8277</t>
+          <t>1940; 8369</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2487; 9635</t>
+          <t>2472; 9522</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3933; 13202</t>
+          <t>4063; 13357</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>542; 6577</t>
+          <t>0; 6055</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4544; 12942</t>
+          <t>4629; 12969</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8700; 20252</t>
+          <t>8818; 20399</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6896; 19124</t>
+          <t>7191; 20137</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>791; 7293</t>
+          <t>725; 7480</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3132; 10977</t>
+          <t>3153; 10916</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7608; 17821</t>
+          <t>7495; 17889</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4770; 13225</t>
+          <t>4309; 12886</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1273; 7309</t>
+          <t>1339; 7858</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1356; 7451</t>
+          <t>1352; 7437</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12251; 24595</t>
+          <t>12736; 24318</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7772; 18335</t>
+          <t>7717; 18397</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3226</t>
+          <t>0; 3073</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5891; 15739</t>
+          <t>5580; 15279</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22588; 38325</t>
+          <t>23251; 38973</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13383; 27561</t>
+          <t>14677; 28209</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1486; 8681</t>
+          <t>1484; 9455</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>637; 6330</t>
+          <t>639; 5978</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8313; 19029</t>
+          <t>8401; 18448</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3322; 11801</t>
+          <t>3666; 12126</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4971</t>
+          <t>0; 6189</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>480; 4873</t>
+          <t>479; 4471</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3843; 12085</t>
+          <t>3764; 11825</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3588; 13111</t>
+          <t>3850; 13005</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2036</t>
+          <t>0; 1929</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1806; 8437</t>
+          <t>1890; 8601</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13552; 27099</t>
+          <t>13695; 27133</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8492; 20872</t>
+          <t>8609; 20709</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>362; 5973</t>
+          <t>367; 5810</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>793; 7444</t>
+          <t>728; 6890</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8425; 20003</t>
+          <t>8492; 20197</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7308; 18944</t>
+          <t>6683; 18416</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>669; 6259</t>
+          <t>665; 6015</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1284; 7176</t>
+          <t>1290; 7355</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4235; 13783</t>
+          <t>3708; 13086</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3464; 12577</t>
+          <t>3643; 12241</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 6400</t>
+          <t>0; 6704</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3355; 11456</t>
+          <t>2840; 11823</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15102; 31408</t>
+          <t>14955; 30302</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12964; 28106</t>
+          <t>12835; 28075</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1475; 9422</t>
+          <t>1522; 9083</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10234; 22365</t>
+          <t>9969; 22453</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>37239; 58394</t>
+          <t>38490; 59050</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22477; 40964</t>
+          <t>23288; 41274</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3597; 13483</t>
+          <t>3869; 14270</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8051; 19316</t>
+          <t>7628; 18685</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28717; 48243</t>
+          <t>28856; 48894</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26171; 44589</t>
+          <t>26540; 45214</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2144; 10486</t>
+          <t>2142; 10620</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>20429; 37446</t>
+          <t>20944; 37144</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>72079; 100496</t>
+          <t>72671; 100119</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>54592; 79978</t>
+          <t>54564; 79629</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8490; 21475</t>
+          <t>7381; 20811</t>
         </is>
       </c>
     </row>
